--- a/03_Outputs/all/01_TablasDescriptivas/idx7_gini.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx7_gini.xlsx
@@ -399,7 +399,7 @@
         <v>-0.4592497601725889</v>
       </c>
       <c r="D2">
-        <v>0.06289475801223222</v>
+        <v>0.06289475801223221</v>
       </c>
       <c r="E2">
         <v>-0.667980058203487</v>
